--- a/StructureDefinition-nimodipine-medication-administration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T11:47:40+00:00</t>
+    <t>2026-06-11T14:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medication-administration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:44:28+00:00</t>
+    <t>2026-06-12T09:34:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medication-administration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:34:13+00:00</t>
+    <t>2026-07-01T13:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medication-administration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:43:23+00:00</t>
+    <t>2026-07-09T09:09:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medication-administration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medication-administration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medication-administration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medication-administration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medication-administration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medication-administration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medication-administration-profile.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/nimodipine-medication-administration-profile</t>
+    <t>http://qualityregistry.org/StructureDefinition/nimodipine-medication-administration-profile</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/stroke-medication-administration-profile</t>
+    <t>http://qualityregistry.org/StructureDefinition/stroke-medication-administration-profile</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -466,7 +466,7 @@
     <t>requiredPostAcuteCare</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://tecnomod-um.org/StructureDefinition/required-post-acute-care-ext}
+    <t xml:space="preserve">Extension {http://qualityregistry.org/StructureDefinition/required-post-acute-care-ext}
 </t>
   </si>
   <si>
@@ -482,7 +482,7 @@
     <t>assessmentTiming</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://tecnomod-um.org/StructureDefinition/assessment-timing-ext}
+    <t xml:space="preserve">Extension {http://qualityregistry.org/StructureDefinition/assessment-timing-ext}
 </t>
   </si>
   <si>
@@ -541,7 +541,7 @@
     <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/assessment-timing-ext</t>
+    <t>http://qualityregistry.org/StructureDefinition/assessment-timing-ext</t>
   </si>
   <si>
     <t>Extension.url</t>
@@ -563,7 +563,7 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/nimodipinetiming-vs</t>
+    <t>http://qualityregistry.org/ValueSet/nimodipinetiming-vs</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -701,7 +701,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/not-medication-reason-vs</t>
+    <t>http://qualityregistry.org/ValueSet/not-medication-reason-vs</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -750,7 +750,7 @@
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the medication resource is recommended.  For example, if you require form or lot number, then you must reference the Medication resource.</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/medications-vs</t>
+    <t>http://qualityregistry.org/ValueSet/medications-vs</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -817,7 +817,7 @@
     <t>MedicationAdministration.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/resq-patient-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/resq-patient-profile)
 </t>
   </si>
   <si>
@@ -842,7 +842,7 @@
     <t>MedicationAdministration.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/stroke-encounter-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/stroke-encounter-profile)
 </t>
   </si>
   <si>

--- a/StructureDefinition-nimodipine-medication-administration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medication-administration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -489,7 +489,7 @@
     <t>Assessment or medication timing</t>
   </si>
   <si>
-    <t>Timing category used by medication-administration builders, e.g. insulin within one hour or paracetamol timing. The Python code contains a typo variant tecnomod-um-org; this IG normalizes to tecnomod-um.org.</t>
+    <t>Timing category used by medication-administration builders, e.g. insulin within one hour or paracetamol timing. The Python code contains a typo variant tecnomod-um-org; this IG normalizes it to the qualityregistry.org canonical.</t>
   </si>
   <si>
     <t>MedicationAdministration.extension:assessmentTiming.id</t>

--- a/StructureDefinition-nimodipine-medication-administration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
